--- a/2022 data/excel_outputs/101_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/101_boothwise_data.xlsx
@@ -14,780 +14,1200 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="421">
   <si>
     <t>AC 101 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>####0##0 ##### ###### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ###### #### 2</t>
-  </si>
-  <si>
-    <t>##0##0##### ########## ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##### ########## ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##### ########## ###### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 #### ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ######### #0 #######</t>
-  </si>
-  <si>
-    <t>######## ##0##0##### ###### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>######## ##0##0##### ###### ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>######## ##0##0##### ###### ###### #0##0 3</t>
-  </si>
-  <si>
-    <t>######## ##0##0##### ###### ###### #0##0 4</t>
-  </si>
-  <si>
-    <t>####### #0##0###### #0 ###### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####### #0##0###### ###### ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0######### #0###### ###### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0######### #0###### ###### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0####### ######## #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0####### ######## #0##0 2</t>
-  </si>
-  <si>
-    <t>##0##0##### ####### #### ####### #0##0 1</t>
-  </si>
-  <si>
-    <t>##0##0##### ####### #### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##### #0 #######</t>
-  </si>
-  <si>
-    <t>####0##0###### ### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0######### #0##0 2</t>
-  </si>
-  <si>
-    <t>###### ######### ###### ### #### 1</t>
-  </si>
-  <si>
-    <t>###### ######### ###### ### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### ###### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ###### #### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0######</t>
-  </si>
-  <si>
-    <t>####0##0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0######## #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0######## #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##########</t>
-  </si>
-  <si>
-    <t>####0##0#######</t>
-  </si>
-  <si>
-    <t>####0##0#### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0##########</t>
-  </si>
-  <si>
-    <t>####0##0########</t>
-  </si>
-  <si>
-    <t>####0##0###### #0 ########</t>
-  </si>
-  <si>
-    <t>####0##0#### ### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0#### ###### #0 #### ###</t>
-  </si>
-  <si>
-    <t>####0##0######## #0 #### ###</t>
-  </si>
-  <si>
-    <t>####0##0######### #0 #### ###</t>
-  </si>
-  <si>
-    <t>####0##0##### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###########</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ########</t>
-  </si>
-  <si>
-    <t>####0##0###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0#### #0######## ###### #### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0#### #0######## ###### #### #0##0 2</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ####</t>
-  </si>
-  <si>
-    <t>####0##0######## #0############# #### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0######## #0############# #### #0##02</t>
-  </si>
-  <si>
-    <t>####0##0####### #0######## ##### ####</t>
-  </si>
-  <si>
-    <t>######## #### ## ######## ##### ####</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### #0 #######</t>
-  </si>
-  <si>
-    <t>#### #### ##0######0 ####### ######## ## ##### ####</t>
-  </si>
-  <si>
-    <t>####0##0###### #####</t>
-  </si>
-  <si>
-    <t>####0##0#####</t>
-  </si>
-  <si>
-    <t>####### ##0##0##### ####### ##0##0 1</t>
-  </si>
-  <si>
-    <t>####### ##0##0##### ####### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0###### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0######## ####### ##</t>
-  </si>
-  <si>
-    <t>####0##0####### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0####### #0##0 3</t>
-  </si>
-  <si>
-    <t>#### ####0##0#### #0##0 1</t>
-  </si>
-  <si>
-    <t>#### ####0##0#### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0#### ##### #0 ####</t>
-  </si>
-  <si>
-    <t>####0##0##### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0##### #0##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0##### ##### #### ## ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0##### ##### #### ## ##### ##0 ##02</t>
-  </si>
-  <si>
-    <t>######### #0##0 ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>######### #0##0 ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>######### #0##0 ##### #0##0 3</t>
-  </si>
-  <si>
-    <t>##### #0##0##### ##0##0 1</t>
-  </si>
-  <si>
-    <t>##### #0##0##### #0##0 2</t>
-  </si>
-  <si>
-    <t>##### #0##0##### #0##0 3</t>
-  </si>
-  <si>
-    <t>##### #0##0##### #0##0 4</t>
-  </si>
-  <si>
-    <t>##### #### ######## ##### #0##0 1</t>
-  </si>
-  <si>
-    <t>###### ### ##### #### ######## #####</t>
-  </si>
-  <si>
-    <t>##### #### ######## ##### #0##0 2</t>
-  </si>
-  <si>
-    <t>#### ##### ######## #####</t>
-  </si>
-  <si>
-    <t>######### ###### ##### ##### ## ###### ###</t>
-  </si>
-  <si>
-    <t>######### ###### ##### ##### ## ######## ###</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0###### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0###### #### 2</t>
-  </si>
-  <si>
-    <t>##### ## #####</t>
-  </si>
-  <si>
-    <t>####0##0#### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 #### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0######## #### 1</t>
-  </si>
-  <si>
-    <t>####0##0######## #### 2</t>
-  </si>
-  <si>
-    <t>##0##0##### ######</t>
-  </si>
-  <si>
-    <t>####0##0####</t>
-  </si>
-  <si>
-    <t>####0##0####### ##0#######</t>
-  </si>
-  <si>
-    <t>####0##0 ## #### #######</t>
-  </si>
-  <si>
-    <t>####0##0##### ## ####### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0##### ## ####### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0####### #0 #######</t>
-  </si>
-  <si>
-    <t>#### ####0##0####</t>
-  </si>
-  <si>
-    <t>####0##0 ####</t>
-  </si>
-  <si>
-    <t>####0##0#### ####### ## ####</t>
-  </si>
-  <si>
-    <t>####0##0#0######</t>
-  </si>
-  <si>
-    <t>#0####0##0 #### #0##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0#### ##0##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0#### ##0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0###### #0 #######</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### #######</t>
-  </si>
-  <si>
-    <t>#0####0##0####### #0##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0####### #0##0 2</t>
-  </si>
-  <si>
-    <t>#0####0##0####### #0##0 3</t>
-  </si>
-  <si>
-    <t>#0####0##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0##### #0 #######</t>
-  </si>
-  <si>
-    <t>#0####0##0#######</t>
-  </si>
-  <si>
-    <t>####0##0###### ##0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0###### ##0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### #0 #####</t>
-  </si>
-  <si>
-    <t>####0##0####### #0 #####</t>
-  </si>
-  <si>
-    <t>####0##0###### ### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0###### ### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0###### ### #### 3</t>
-  </si>
-  <si>
-    <t>####0##0#### #### ## ###### ####</t>
-  </si>
-  <si>
-    <t>####0##0###### #0 ######</t>
-  </si>
-  <si>
-    <t>####0##0###### #0 ##########</t>
-  </si>
-  <si>
-    <t>#0####0##0#0### #0##########</t>
-  </si>
-  <si>
-    <t>####0##0######### #0 ##########</t>
-  </si>
-  <si>
-    <t>######### #0 ##### #########</t>
-  </si>
-  <si>
-    <t>####0##0####### #0 ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0####### #0 ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0####### #0 ######</t>
-  </si>
-  <si>
-    <t>#0####0##0##### #######</t>
-  </si>
-  <si>
-    <t>####0##0###### #0 ##### #######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ######</t>
-  </si>
-  <si>
-    <t>####0##0#### ### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0#### ### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### #0 #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #####</t>
-  </si>
-  <si>
-    <t>####0##0##### ###### #0##0 1</t>
-  </si>
-  <si>
-    <t>####0##0##### ###### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0##### ###### #0##0 3</t>
-  </si>
-  <si>
-    <t>####0##0###### #0 ##### ###### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0###### #0 ##### ###### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0###### #0 ##### ######</t>
-  </si>
-  <si>
-    <t>####0##0 #########</t>
-  </si>
-  <si>
-    <t>#0####0##0#### #0##0 1</t>
-  </si>
-  <si>
-    <t>#0####0##0#### #0##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #####</t>
-  </si>
-  <si>
-    <t>####0##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0 #### #0#0 1</t>
-  </si>
-  <si>
-    <t>####0##0 #### #0#0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### #0 ##########</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### #0 ######## ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0 ######## ######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ### #0 ### #### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 #### ### #0 ### #### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0 ###### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0 ###### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0 ######</t>
-  </si>
-  <si>
-    <t>######### #0##0##0 ####### #0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##### #0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####</t>
-  </si>
-  <si>
-    <t>###### ## #######</t>
-  </si>
-  <si>
-    <t>##0##0##### #### #0 ######### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>####0#0 ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>####0#0 ##### #0#0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0#0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0#0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0 ###### #0#0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0 ###### #0#0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0 ###### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0 ###### ######</t>
-  </si>
-  <si>
-    <t>##0##0##### ###### #0 ###### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###</t>
-  </si>
-  <si>
-    <t>######## ########</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0#0 3</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0#0 4</t>
-  </si>
-  <si>
-    <t>######## #0##0 ###### #0#0 1</t>
-  </si>
-  <si>
-    <t>######## #0##0 ###### #0#0 2</t>
-  </si>
-  <si>
-    <t>######## #0##0 ###### #0#0 3</t>
-  </si>
-  <si>
-    <t>######## #0##0 ###### #0#0 4</t>
-  </si>
-  <si>
-    <t>######## #0##0 ###### #0#0 5</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ########</t>
-  </si>
-  <si>
-    <t>####0##0 #### ## #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 #### ## #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0 #### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ### #0 #### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0 #### #######</t>
-  </si>
-  <si>
-    <t>####0##0 #### #0 #### #######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ### #0 ##### #######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ######## #0 ##### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ############</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0#0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0#0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>#### ######## ######0 #### ###### #0 #####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0 #####</t>
-  </si>
-  <si>
-    <t>##### ##### ##### #####</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### 2</t>
-  </si>
-  <si>
-    <t>##0##0##### ########</t>
-  </si>
-  <si>
-    <t>###### ####0######## ##### #0#0 1</t>
-  </si>
-  <si>
-    <t>###### ####0######## ##### #0#0 2</t>
-  </si>
-  <si>
-    <t>##0##0##0##### #### #### #0 ######### ######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ######### #0 ######### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0 ######### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ####0######## #### ##### #0 ######### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ### #0#0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ### #0#0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### #########</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### ## ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #0####### #0#0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #0####### #0#0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ####### #0#0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ####### #0#0 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### #0 ;#####ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #######</t>
-  </si>
-  <si>
-    <t>##0##0##### ####### #0#0 1</t>
-  </si>
-  <si>
-    <t>##0##0##### ####### #0#0 2</t>
-  </si>
-  <si>
-    <t>##0##0##### ####### #0#0 3</t>
-  </si>
-  <si>
-    <t>##0##0##### ####### #0#0 4</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #0#0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #0#0 2</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ######### ##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0 #### ### ## #####</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ## ###### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ## ####### #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ###### #0#0 1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ###### #0#0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ######## #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ######## #### 2</t>
+    <t>A0PA0 BAGHELA PU TA</t>
+  </si>
+  <si>
+    <t>JU0HA0 KUL CH PARU A GAUPARU A K0NAM0 1</t>
+  </si>
+  <si>
+    <t>JU0HA0 KUL CH PARU A GAUPARU A K0NAM0 2</t>
+  </si>
+  <si>
+    <t>JU0HA0 KUL CH PARU A GAUPARU A K0NAM0 3</t>
+  </si>
+  <si>
+    <t>NAV N MAT A0PA0 DATALANA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>NAV N MAT A0PA0 DATALANA K0N0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 UDHAI R PU TA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 UDHAI R PU TA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 TUM"RAYA</t>
+  </si>
+  <si>
+    <t>A0PA0 NAGALA RAMACH M0 TUM"RAYA</t>
+  </si>
+  <si>
+    <t>GAMGE$VAR JU0HA0 KUL MANAPUR NAG"RAYA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>GAMGE$VAR JU0HA0 KUL MANAPUR NAG"RAYA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>GAMGE$VAR JU0HA0 MANAPARU NAG"RAYA K0NAM0 3</t>
+  </si>
+  <si>
+    <t>GAMGE$VAR JU0HA0 MANAPARU NAG"RAYA K0NAM0 4</t>
+  </si>
+  <si>
+    <t>SHERAVANI I0KA0 YAUL) M0 MANAPUR NAG"RAYA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>SHERAVANI I0KA0 YAUL) MANAPUR NAG"RAYA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 MAJAPARU M0MANAPARU NAG"RAYA</t>
+  </si>
+  <si>
+    <t>A0PA0MAUJAMAPARU HUSAINAPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0MAUJAMAPARU HUSAINAPARU K0NAM0 2</t>
+  </si>
+  <si>
+    <t>JU0HA0GADARAPARU A MAJARA VASAP U RU A K0NAM0 1</t>
+  </si>
+  <si>
+    <t>JU0HA0 KUL GADARAPARU A MAJARA VASAP U RU A K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 GALA KAIYAM M0 BASAP U RU A</t>
+  </si>
+  <si>
+    <t>A0PA0M-HAR NAGAR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0M-HARANAGAR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0M-HAR NAGAR K0NAM0 3</t>
+  </si>
+  <si>
+    <t>A0PA0M-HAR NAGAR K0NAM0 4</t>
+  </si>
+  <si>
+    <t>A0PA0 PATANA MAJARA RAYAPARU PATANA</t>
+  </si>
+  <si>
+    <t>A0PA0 RAYAPARU MAJARA RAYAPARU PATANA</t>
+  </si>
+  <si>
+    <t>A0PA0 GUDAGUDI</t>
+  </si>
+  <si>
+    <t>A0PA0BHARATAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 HASANAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 YAUL)</t>
+  </si>
+  <si>
+    <t>A0PA0 CHAMDAVA PU TA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 CHAMDAVA PU TA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0M NAKAPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0M NAKAPARU K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 MAJ U PHAPHAR NAGAR</t>
+  </si>
+  <si>
+    <t>A0PA0MAMGADAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0NAGALA VADAN</t>
+  </si>
+  <si>
+    <t>NAV N0 A0PA0 BAJANAGAR SAPHED</t>
+  </si>
+  <si>
+    <t>A0PA0MAUH1MADAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0KAMU VARAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0NAUGAVAM M0 KAMU VARAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0ROSHAN NAGAR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0ROSHANANAGAR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>NAV N MAT A0PA0NAM0 I$VAR) M0 ROSHAN NAGAR</t>
+  </si>
+  <si>
+    <t>A0PA0 YARAPARU M0 ROSHAN NAGAR</t>
+  </si>
+  <si>
+    <t>A0PA0GAMD U RAGAMJ M0 ROSHAN NAGAR</t>
+  </si>
+  <si>
+    <t>A0PA0D)PAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0G3DHAYA 3HAMOL)</t>
+  </si>
+  <si>
+    <t>A0PA0TARAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 A-HAD)NAPARU</t>
+  </si>
+  <si>
+    <t>U55A A06V7YALAY KHA LAKAPARU</t>
+  </si>
+  <si>
+    <t>A06V0 BHALAUL) K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 BHALAUL) K0N0 2</t>
+  </si>
+  <si>
+    <t>A0PA0TAL) M0L MIPUR SU DAR SAMH K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0TAL) M0L MIPUR SU DAR SAMH K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0YAKUTAGAMJ M0L MIPURAGOPAL SAMH K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0YAKUTAGAMJ M0L MIPURAGOPAL SAMH K0NAM02</t>
+  </si>
+  <si>
+    <t>A0PA0PHAR)DAPARU M0L MIPARU GOPAL SAMH</t>
+  </si>
+  <si>
+    <t>A0PA0NAM0HAM SI M0 MIRAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0RAJAPARU A</t>
+  </si>
+  <si>
+    <t>A0PA0BADHAR)KALॉ</t>
+  </si>
+  <si>
+    <t>JANATA U0MA06V7YALAY BADHAR) KALॉ BHANAP U RU A</t>
+  </si>
+  <si>
+    <t>A0PA0SHEKHAPARU NARAI</t>
+  </si>
+  <si>
+    <t>A0PA0LALAP U RU A</t>
+  </si>
+  <si>
+    <t>A0PA0CHAMDI</t>
+  </si>
+  <si>
+    <t>A0PA0NABAVAGAMJ</t>
+  </si>
+  <si>
+    <t>AMARAG: U JU0HA0 KUL NABAVAGAMJ KAM0NAM0 1</t>
+  </si>
+  <si>
+    <t>AMARAG: U JU0HA0 KUL NABAVAGAMJ K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0BADAGॉV K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0BADAGॉV K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0PARATAPAPARU MAUH1MAD KHA◌.C</t>
+  </si>
+  <si>
+    <t>A0PA0CHॉDAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0JAMALAPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0JAMALAPARU K0NAM0 2</t>
+  </si>
+  <si>
+    <t>U5CH A06V0BAUDAR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>U5CH A06V0BAUDAR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0NAGALA M3DHAYA M0 BAUDAR</t>
+  </si>
+  <si>
+    <t>A0PA0SAHAVAR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0SAHAVAR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>K0 A0PA0SAHAVAR TE T B=K KE SAMANE K0NAM0 1</t>
+  </si>
+  <si>
+    <t>K0 A0PA0SAHAVAR TE T B=K KE SAMANE KAM0 NAM02</t>
+  </si>
+  <si>
+    <t>I LA MAYAM I0KA0 SAHAVAR K0NAM0 1</t>
+  </si>
+  <si>
+    <t>I LA MAYAM I0KA0 SAHAVAR KAM0NAM0 2</t>
+  </si>
+  <si>
+    <t>I LA MAYAM I0KA0 SAHAVAR KAM0NAM0 3</t>
+  </si>
+  <si>
+    <t>GAMDHI I0KA0SAHAVAR KAM0NAM0 1</t>
+  </si>
+  <si>
+    <t>GAMDHI I0KA0SAHAVAR K0NAM0 2</t>
+  </si>
+  <si>
+    <t>GAMDHI I0KA0SAHAVAR K0NAM0 3</t>
+  </si>
+  <si>
+    <t>GAMDHI I0KA0SAHAVAR K0NAM0 4</t>
+  </si>
+  <si>
+    <t>SHRAKL|AIBHTBBH|KLDYACH AIBHTBBHDYAJBH|THABHS|THABHSHRCH AIBHTBBH|KL|AIKL|PKL|AI DYACHKL|JBH|THABHKL|SHRAKL|SHR AIBHTBBH0THATHABHKL|J~N0 1</t>
+  </si>
+  <si>
+    <t>J~NADYABBHJ~N3AIBHT|KL|AI JBH|THABHKL|P 6SHRAKL|AIBHTBBH|KLDYACH AIBHTBBHDYAJBH|THABHS|THABHSHRCH AIBHTBBH|KL|AIKL|PKL|AI DYACHKL|JBH|THABHKL|SHRAKL|SHR</t>
+  </si>
+  <si>
+    <t>SHRAKL|AIBHTBBH|KLDYACH AIBHTBBHDYAJBH|THABHS|THABHSHRCH AIBHTBBH|KL|AIKL|PKL|AI DYACHKL|JBH|THABHKL|SHRAKL|SHR AIBHTBBH0THATHABHKL|J~N0 2</t>
+  </si>
+  <si>
+    <t>TAUN E"RAYA KAYALAY SAHAVAR</t>
+  </si>
+  <si>
+    <t>AEBIY SAHAKAR) S M T SAHAVAR KE BARAMADE MAC</t>
+  </si>
+  <si>
+    <t>AEBIY SAHAKAR) S M T SAHAVAR KE KAYALAY MAC</t>
+  </si>
+  <si>
+    <t>A0PA0 GUNAR</t>
+  </si>
+  <si>
+    <t>A0PA0TAJAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0JAUHAR)</t>
+  </si>
+  <si>
+    <t>A0PA0KANOI K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 KANOI K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0SA3DAKAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0RAYAD</t>
+  </si>
+  <si>
+    <t>JU0HA0 KUL CHATAUNI</t>
+  </si>
+  <si>
+    <t>A0PA0RARA</t>
+  </si>
+  <si>
+    <t>A0PA0PHATEHAPARU TA0MOHANAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0MAU M0 B TARAMAU</t>
+  </si>
+  <si>
+    <t>A0PA0 NAGALA DE VI M0 B TARAMAU</t>
+  </si>
+  <si>
+    <t>A0PA0B TAR MAJARA B TARAMAU</t>
+  </si>
+  <si>
+    <t>A0PA0JALALAPUR M0 B TARAMAU</t>
+  </si>
+  <si>
+    <t>A0PA0KHARAPARA</t>
+  </si>
+  <si>
+    <t>A0PA0BAHARAPUR</t>
+  </si>
+  <si>
+    <t>U5CH A06V0JAIDHAR</t>
+  </si>
+  <si>
+    <t>A0PA0 LAHARA</t>
+  </si>
+  <si>
+    <t>A0PA0N0UMED M0 LAHARA</t>
+  </si>
+  <si>
+    <t>A0PA0NAGALA LAFMAN MAJARA LAHARA</t>
+  </si>
+  <si>
+    <t>A0PA0N0NAINASAKH U</t>
+  </si>
+  <si>
+    <t>A0PA0PADARATHAPUR</t>
+  </si>
+  <si>
+    <t>U0 A06V0 GADHAKA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>U0 A06V0GADHAKA KAM0NAM0 2</t>
+  </si>
+  <si>
+    <t>U0 A06V0GADHAKA KAM0NAM0 3</t>
+  </si>
+  <si>
+    <t>A0PA0HASANAPUR M0 6PATHANAPUR</t>
+  </si>
+  <si>
+    <t>A0PA0 6VAHMAPARU MAJARA 6PATHANAPARU</t>
+  </si>
+  <si>
+    <t>U0 A06V0SEVANAPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>U0 A06V0SEVANAPARU K0NAM0 2</t>
+  </si>
+  <si>
+    <t>U0 A06V0 EGAVAM</t>
+  </si>
+  <si>
+    <t>A0PA0GANESHAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0NATHAP U RU</t>
+  </si>
+  <si>
+    <t>A0PA0NAUPATI M0 NATHAP U RU</t>
+  </si>
+  <si>
+    <t>U0 A06V0ABHAP U RU A</t>
+  </si>
+  <si>
+    <t>A0PA0IKHATAUL) KAM0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0IKHATAUL) KAM0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0SARASAVA</t>
+  </si>
+  <si>
+    <t>A0PA0NAM0MOHAN M0 SARASAVA</t>
+  </si>
+  <si>
+    <t>A0PA0PHARAUL) K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0PHARAUL) K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0KHAD U ATAL M0 PHARAUL)</t>
+  </si>
+  <si>
+    <t>A0PA0S=TI</t>
+  </si>
+  <si>
+    <t>A0PA0BINAPARU KALॉ UJTAR)</t>
+  </si>
+  <si>
+    <t>A0PA0BINAPARU KALॉ DAKANI</t>
+  </si>
+  <si>
+    <t>A0PA0NAGALA TAL)</t>
+  </si>
+  <si>
+    <t>A0PA0A MARASA</t>
+  </si>
+  <si>
+    <t>A0PA0RAMANAGAR M0 A MARASA</t>
+  </si>
+  <si>
+    <t>A0PA0NAG"RAYA M0 BODANAG"RAYA</t>
+  </si>
+  <si>
+    <t>U0 A06V0N0BHUD M0BODANAG"RAYA</t>
+  </si>
+  <si>
+    <t>A0PA0K LAYANAPARU M0 BODANAG"RAYA</t>
+  </si>
+  <si>
+    <t>A0PA0ITAVARAPARU</t>
+  </si>
+  <si>
+    <t>CH0I0KALEJ JAHॉGIRAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0IM LAYA M0 KHOJAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0KHOJAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0H)RAPARU M0 KHOJAPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0H)RAPARU M0 KHOJAPARU K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0BAMJAR) M0 KHOJAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0BAHAPARU M0 KHOJAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0N0NAHAR M0 KHOJAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0UDARANAPARU M0 KHOJAPARU</t>
+  </si>
+  <si>
+    <t>U0 A06V0 MADAUL BAJ U UG</t>
+  </si>
+  <si>
+    <t>A0PA0DHAKAPARU A M0 MADAUL BAJ U UG</t>
+  </si>
+  <si>
+    <t>A0PA0BHAJ U PARU A</t>
+  </si>
+  <si>
+    <t>A0PA0KODARA</t>
+  </si>
+  <si>
+    <t>A0PA0SARAUTHAN</t>
+  </si>
+  <si>
+    <t>A0PA0N0KU DAN</t>
+  </si>
+  <si>
+    <t>A0PA0SARASAI N:</t>
+  </si>
+  <si>
+    <t>A0PA0RAMAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 THARACHITARA</t>
+  </si>
+  <si>
+    <t>A0PA0 NAMGALA HATHI M0 BHADER)</t>
+  </si>
+  <si>
+    <t>U0 A06V0BHADER)</t>
+  </si>
+  <si>
+    <t>A0PA0KACHE LA SHERAPARU K0NAM0 1</t>
+  </si>
+  <si>
+    <t>A0PA0KACHE LA SHERAPARU K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0BUDATHARA M0 KACHE LA SHERAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0SHERAPARU M0 KACHE LA SHERAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 YADAGARAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0BASAVANAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0BAHATA</t>
+  </si>
+  <si>
+    <t>U0 A06V0BAHATA K0NAM0 1</t>
+  </si>
+  <si>
+    <t>U0 A06V0BAHATA K0NAM0 2</t>
+  </si>
+  <si>
+    <t>A0PA0SAJ U ANAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 MAV U A"RAKAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 BADHAR) KHAD U</t>
+  </si>
+  <si>
+    <t>A0PA0 MAJIDAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 NIMAR)</t>
+  </si>
+  <si>
+    <t>A0PA0 RE KHAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 SAILAI K0N0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 SAILAI K0N0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 OKASHORAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 D:APARU</t>
+  </si>
+  <si>
+    <t>A0PA0 NAGALA SAHAJAN M0 MUNAQVARAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 NAGALA KOTHAN M0 KAS MAPARU MAHAR)</t>
+  </si>
+  <si>
+    <t>A0PA0 MAHAR) M0 KA SAMAPARU MAHAR)</t>
+  </si>
+  <si>
+    <t>A0PA0 3DAHAR) M0 KA MASAPARU MAHAR)</t>
+  </si>
+  <si>
+    <t>A0PA0 NAGALA SAMAS M0 BAR) KHEDA</t>
+  </si>
+  <si>
+    <t>A0PA0 SARU TAPARU M0 KHUSHAKAR)</t>
+  </si>
+  <si>
+    <t>A0PA0 ARAHARAPARU M0 KHUSHAKAR)</t>
+  </si>
+  <si>
+    <t>SA0U0MA06V0 BABAP U RU M0 KHUSHAKAR)</t>
+  </si>
+  <si>
+    <t>A0PA0 NAGALA KAT)LA M0 KHUSHAKAR)</t>
+  </si>
+  <si>
+    <t>A0PA0 L MIPARU M0 KHUSHAKAR)</t>
+  </si>
+  <si>
+    <t>A0PA0 BAJIRAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 PHARROJAPARU SANI</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT GHAR MAHE SHAPARU</t>
+  </si>
+  <si>
+    <t>JU0HA0 KUL MAIYॉ M0 GAC DAP U RU A GOVADHAN</t>
+  </si>
+  <si>
+    <t>A0PA0 GAC DAP U RU A PADAM SAMH</t>
+  </si>
+  <si>
+    <t>A0PA0 MAHADAVA K0N0 1</t>
+  </si>
+  <si>
+    <t>A0P0 MAHADAVA K0N0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 KARASANA K0N0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 KARASANA K0N0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 KAMALAPARU M0 KARASANA K0N0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 KAMALAPARU M0 KARASANA K0N0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 TODARAPARU M0 KARASANA</t>
+  </si>
+  <si>
+    <t>A0PA0 DE VAR)</t>
+  </si>
+  <si>
+    <t>A0PA0 BHARATAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 LODHIPARU M0 SAMASAPARU DACGAR)</t>
+  </si>
+  <si>
+    <t>NAV N MAT A0PA0 SAMASAPARU DEGAR)</t>
+  </si>
+  <si>
+    <t>KL0THATHABHKL0 JBH|THABHBBH|S|THABHSHRCH|KL J~N0 DYACHJBH|THABHK|AIBHTBBHDYAJBH|THABHKL|THATHABHKL|SHRABBH JBH|THABHBBH|S|THABHSHRCH|KL</t>
+  </si>
+  <si>
+    <t>|PTHABHJDYABBH0JBH|THABHKL0 AIBHTBBHDYABBH|P DYACHJBH|THABHK|AIBHTBBHDYAJBH|THABHKL|THATHABHKL|SHRABBH J~N0 DYACHJBH|THABHK|AIBHTBBHDYAJBH|THABHKL|THATHABHKL|SHRABBH JBH|THABHBBH|S|THABHSHRCH|KL</t>
+  </si>
+  <si>
+    <t>A0PA0 JAKHA</t>
+  </si>
+  <si>
+    <t>PAMCHAYAT GHAR L MIPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 CHAUPARA</t>
+  </si>
+  <si>
+    <t>A0PA0 AMॉPARU K0N0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 AMॉPARU K0N0 2</t>
+  </si>
+  <si>
+    <t>MASKHANALAL I0KA0 AMॉPARU K0N0 1</t>
+  </si>
+  <si>
+    <t>MASKHANALAL I0KA0 AMॉPARU K0N0 2</t>
+  </si>
+  <si>
+    <t>MASKHANALAL I0KA0 AMॉPARU K0N0 3</t>
+  </si>
+  <si>
+    <t>MASKHANALAL I0KA0 AMॉPARU K0N0 4</t>
+  </si>
+  <si>
+    <t>MASKHANALAL I0KA0 AMॉPARU K0N0 5</t>
+  </si>
+  <si>
+    <t>MASKHANALAL I0KA0 AMॉPARU K0N0 6</t>
+  </si>
+  <si>
+    <t>MASKHANALAL I0KA0 AMॉPARU K0N0 7</t>
+  </si>
+  <si>
+    <t>A0PA0 BANAP U RU A BASKALAN</t>
+  </si>
+  <si>
+    <t>A0PA0 BARANAGAR</t>
+  </si>
+  <si>
+    <t>A0PA0 SARASAI VAN</t>
+  </si>
+  <si>
+    <t>A0PA0 SARASAIT</t>
+  </si>
+  <si>
+    <t>A0PA0 RANAMAU K0N0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 RANAMAU K0N0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 BHAGAP U RU A</t>
+  </si>
+  <si>
+    <t>A0PA0 VADADAP U RU</t>
+  </si>
+  <si>
+    <t>A0PA0 AN DAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 NAGALA KHAR)</t>
+  </si>
+  <si>
+    <t>A0PA0 DE VAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 KADDHA</t>
+  </si>
+  <si>
+    <t>A0PA0 VIRAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 PARATAPAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 VACHAMAI</t>
+  </si>
+  <si>
+    <t>A0PA0 VAYAL)</t>
+  </si>
+  <si>
+    <t>A0PA0 6VAKORA</t>
+  </si>
+  <si>
+    <t>A0PA0 ISHEPARU M0 JATAU ASHOKAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 MUNIR NAGAR M0 JATAU ASHOKAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 ASHOKAPARU M0 JATAU ASHOKAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 JATAU M0 JATAU ASHOKAPARU</t>
+  </si>
+  <si>
+    <t>U5CH0 A06V0 NAGALA YADAKARAN M0 JATAU ASHOKAPUR</t>
+  </si>
+  <si>
+    <t>A0PA0 NAGALA BAS M0 RASALUA SAL U HAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 NAGALA ANASAKH U M0 RASALUA SAL U HAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 DORA</t>
+  </si>
+  <si>
+    <t>A0PA0 SAK ABAD</t>
+  </si>
+  <si>
+    <t>A0PA0 JAVAHARAPARU M0 SAK ABAD</t>
+  </si>
+  <si>
+    <t>A0PA0 TGAVA SANI</t>
+  </si>
+  <si>
+    <t>A0PA0 MAJHOLA</t>
+  </si>
+  <si>
+    <t>A0PA0 ABHAYAPARU A K0N0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 ABHAYAPARU A K0N0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 PHAKAUTA</t>
+  </si>
+  <si>
+    <t>A0PA0 SHERAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 NADARAMAI K0N0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 NADARAMAI K0N0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 BARASAUDA</t>
+  </si>
+  <si>
+    <t>A0PA0 JIMGAN</t>
+  </si>
+  <si>
+    <t>A0PA0 NARAI</t>
+  </si>
+  <si>
+    <t>U5CH ATH MAK 6V7YA0 NAGALA MAHAJAV M0 NARAI</t>
+  </si>
+  <si>
+    <t>A0PA0 AWTAPARU M0 NARAI</t>
+  </si>
+  <si>
+    <t>|PCHAJBH|THABHDY|PTHABH CHLABHSHRADYAJ SHRCHADYAIDAIBHT BBHDYACHASॉJ</t>
+  </si>
+  <si>
+    <t>A0PA0 LI5CHAMAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 JARAI</t>
+  </si>
+  <si>
+    <t>A0PA0 3TAKU"RAYA</t>
+  </si>
+  <si>
+    <t>JU0HA0 KUL A-L)PARU</t>
+  </si>
+  <si>
+    <t>U5CHATAR A06V7YALAY SEVAKA K0N0 1</t>
+  </si>
+  <si>
+    <t>U5CHATAR A06V7YALAY SEVAKA K0N0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 SAJ U RAI</t>
+  </si>
+  <si>
+    <t>A0PA0 B NAYAL) M0 SAJ U RAI</t>
+  </si>
+  <si>
+    <t>RA0JU0HA0 KUL NAGALA OKASHAN M0 AJUNAPUR NAUABAD</t>
+  </si>
+  <si>
+    <t>A0PA0 NAGALA I JIT M0 AJUNAPUR NAUABAD</t>
+  </si>
+  <si>
+    <t>A0PA0 SHAHAPARU M0 AJUNAPARU NAUABAD</t>
+  </si>
+  <si>
+    <t>A0PA0 AJUNAPARU KAD)M</t>
+  </si>
+  <si>
+    <t>U5CH A06V7YALAY NAGALA BHAVANI M0 AJUNAPUR KAD)M</t>
+  </si>
+  <si>
+    <t>A0PA0 THANAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 SEMARA MOCHA</t>
+  </si>
+  <si>
+    <t>A0PA0 HARAJAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 HAM SAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 NAG"RAYA</t>
+  </si>
+  <si>
+    <t>A0PA0 UCHAGॉV</t>
+  </si>
+  <si>
+    <t>|0CH|0 DAGHK|CH|CH|TN</t>
+  </si>
+  <si>
+    <t>A0PA0 BASAI K0N0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 BASAI K0N0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 NAGALA PATAVAR)AN</t>
+  </si>
+  <si>
+    <t>A0PA0 GOPALAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 ALAMAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 NAGALA KOTHAN M0 SARASAUL</t>
+  </si>
+  <si>
+    <t>A0PA0 SARASOL</t>
+  </si>
+  <si>
+    <t>A0PA0 SANAUTH</t>
+  </si>
+  <si>
+    <t>A0PA0 KARAMAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 MAJAKH U RU )</t>
+  </si>
+  <si>
+    <t>A0PA0 RAM JITAPARU</t>
+  </si>
+  <si>
+    <t>|0CH|0 KBHKHN TH|L|P</t>
+  </si>
+  <si>
+    <t>A0PA0 BAHORANAPARU M0DH6U VAYAI</t>
+  </si>
+  <si>
+    <t>A0PA0 SAKAHARA K0N0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 SAKAHARA K0N0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 DHA"RAKAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 BAMSI</t>
+  </si>
+  <si>
+    <t>A0PA0 LAKHANAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 KHARAGATIPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 RAJAMAU</t>
+  </si>
+  <si>
+    <t>A0PA0 TAJAPARU PAV U</t>
+  </si>
+  <si>
+    <t>A0PA0 TAJAPARU P$I◌CHAM</t>
+  </si>
+  <si>
+    <t>A0PA0 DE HAL) BAJ U UG</t>
+  </si>
+  <si>
+    <t>A0PA0 A-HE DADAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 SAMHAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 NAGALA KHAMJAN M0 (SUNAVAI)</t>
+  </si>
+  <si>
+    <t>A0PA0 \GALOL)</t>
+  </si>
+  <si>
+    <t>A0PA0 A TAU MAMGADAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 MAMGADAPARU</t>
+  </si>
+  <si>
+    <t>JU0HA0 KUL MOHANAPARU K0N0 1</t>
+  </si>
+  <si>
+    <t>JU0HA0 KUL MOHANAPARU K0N0 2</t>
+  </si>
+  <si>
+    <t>JU0HA0 KUL MOHANAPARU K0N0 3</t>
+  </si>
+  <si>
+    <t>A0PA0 MOHANAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 MATE NA</t>
+  </si>
+  <si>
+    <t>A0PA0 SAROR)</t>
+  </si>
+  <si>
+    <t>A0PA0 NAGALA BHIMASAIN</t>
+  </si>
+  <si>
+    <t>A0PA0 6PALAKHUNI UJTAR</t>
+  </si>
+  <si>
+    <t>A0PA0 6PALAKHUNI P$I◌CHAM</t>
+  </si>
+  <si>
+    <t>A0PA0 MADHAP U RU A</t>
+  </si>
+  <si>
+    <t>A0PA0 THATHAN</t>
+  </si>
+  <si>
+    <t>A0PA0 DHAN SAMHAPARU K0N0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 DHAN SAMHAPARU K0N0 2</t>
+  </si>
+  <si>
+    <t>JU0HA0 KUL B-HARAPARU TA0 6P\THANAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 BHOGAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 6PATHANAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 DAMAR)</t>
+  </si>
+  <si>
+    <t>A0PA0 NAGALA MOD M0 DAMAR)</t>
+  </si>
+  <si>
+    <t>A0PA0 ANAMGAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 RAMANAGAR</t>
+  </si>
+  <si>
+    <t>A0PA0 RAYAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 MAGATHARA K0N0 1</t>
+  </si>
+  <si>
+    <t>A0PA0 MAGATHARA K0N0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 MEMADA M0 CHॉDAPARU MEMADA</t>
+  </si>
+  <si>
+    <t>M RU MEMADA A0PA0 CHॉDAPARU M0 CHॉDAP</t>
+  </si>
+  <si>
+    <t>U5CHATAR ATH MAK 6V7YALAY BAKAVAL) K0N0 1</t>
+  </si>
+  <si>
+    <t>U5CHATAR ATH MAK 6V7YALAY BAKAVAL) K0N0 2</t>
+  </si>
+  <si>
+    <t>A0PA0 S- U TANAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM NO. 346</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM NO. 347</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM NO. 348</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM NO. 349</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM NO. 350</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM NO. 351</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 352</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 353</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 354</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 355</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 356</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 357</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 358</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 359</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 360</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 361</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 362</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 363</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 364</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 365</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 366</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 367</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 368</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 369</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 370</t>
+  </si>
+  <si>
+    <t>A0PA0 JAL)LAPARU $YAMAPARU ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 371</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -863,8 +1283,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -880,7 +1308,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -888,12 +1316,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1192,85 +1638,157 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>258</v>
+        <v>398</v>
       </c>
       <c r="D2" t="s">
-        <v>259</v>
+        <v>399</v>
       </c>
       <c r="E2" t="s">
-        <v>260</v>
+        <v>400</v>
       </c>
       <c r="F2" t="s">
-        <v>261</v>
+        <v>401</v>
       </c>
       <c r="G2" t="s">
-        <v>262</v>
+        <v>402</v>
       </c>
       <c r="H2" t="s">
-        <v>263</v>
+        <v>403</v>
       </c>
       <c r="I2" t="s">
-        <v>264</v>
+        <v>404</v>
       </c>
       <c r="J2" t="s">
-        <v>265</v>
+        <v>405</v>
       </c>
       <c r="K2" t="s">
-        <v>266</v>
+        <v>406</v>
       </c>
       <c r="L2" t="s">
-        <v>267</v>
+        <v>407</v>
       </c>
       <c r="M2" t="s">
-        <v>268</v>
+        <v>408</v>
       </c>
       <c r="N2" t="s">
-        <v>269</v>
+        <v>409</v>
       </c>
       <c r="O2" t="s">
-        <v>270</v>
+        <v>410</v>
       </c>
       <c r="P2" t="s">
-        <v>271</v>
+        <v>411</v>
       </c>
       <c r="Q2" t="s">
-        <v>272</v>
+        <v>412</v>
       </c>
       <c r="R2" t="s">
-        <v>273</v>
+        <v>413</v>
       </c>
       <c r="S2" t="s">
-        <v>274</v>
+        <v>414</v>
       </c>
       <c r="T2" t="s">
-        <v>275</v>
+        <v>415</v>
       </c>
       <c r="U2" t="s">
-        <v>276</v>
+        <v>416</v>
       </c>
       <c r="V2" t="s">
-        <v>277</v>
+        <v>417</v>
       </c>
       <c r="W2" t="s">
-        <v>278</v>
+        <v>418</v>
       </c>
       <c r="X2" t="s">
-        <v>279</v>
+        <v>419</v>
       </c>
       <c r="Y2" t="s">
-        <v>280</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1278,7 +1796,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1355,7 +1873,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1432,7 +1950,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1509,7 +2027,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1586,7 +2104,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1663,7 +2181,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1740,7 +2258,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1817,7 +2335,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1894,7 +2412,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1971,7 +2489,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -2048,7 +2566,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -2125,7 +2643,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -2202,7 +2720,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -2279,7 +2797,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -2356,7 +2874,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -2433,7 +2951,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -2510,7 +3028,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2587,7 +3105,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -2664,7 +3182,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2741,7 +3259,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -2818,7 +3336,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2895,7 +3413,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -2972,7 +3490,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -3049,7 +3567,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -3126,7 +3644,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -3203,7 +3721,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -3280,7 +3798,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3357,7 +3875,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -3434,7 +3952,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -3511,7 +4029,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -3588,7 +4106,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -3665,7 +4183,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -3742,7 +4260,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -3819,7 +4337,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -3896,7 +4414,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -3973,7 +4491,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -4050,7 +4568,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -4127,7 +4645,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -4204,7 +4722,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -4281,7 +4799,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -4358,7 +4876,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -4435,7 +4953,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -4512,7 +5030,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -4589,7 +5107,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -4666,7 +5184,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -4743,7 +5261,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -4820,7 +5338,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -4897,7 +5415,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -4974,7 +5492,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -5051,7 +5569,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -5128,7 +5646,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -5205,7 +5723,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -5282,7 +5800,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -5359,7 +5877,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -5436,7 +5954,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -5513,7 +6031,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -5590,7 +6108,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -5667,7 +6185,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -5744,7 +6262,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -5821,7 +6339,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -5898,7 +6416,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -5975,7 +6493,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -6052,7 +6570,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -6129,7 +6647,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -6206,7 +6724,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -6283,7 +6801,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -6360,7 +6878,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -6437,7 +6955,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -6514,7 +7032,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -6591,7 +7109,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -6668,7 +7186,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -6745,7 +7263,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -6822,7 +7340,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -6899,7 +7417,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -6976,7 +7494,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -7053,7 +7571,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -7130,7 +7648,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -7207,7 +7725,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -7284,7 +7802,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -7361,7 +7879,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -7438,7 +7956,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -7515,7 +8033,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -7592,7 +8110,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -7669,7 +8187,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -7746,7 +8264,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -7823,7 +8341,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -7900,7 +8418,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -7977,7 +8495,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -8054,7 +8572,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -8131,7 +8649,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -8208,7 +8726,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -8285,7 +8803,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -8362,7 +8880,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -8439,7 +8957,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -8516,7 +9034,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -8593,7 +9111,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -8670,7 +9188,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -8747,7 +9265,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -8824,7 +9342,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -8901,7 +9419,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -8978,7 +9496,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -9055,7 +9573,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -9132,7 +9650,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -9209,7 +9727,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -9286,7 +9804,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -9363,7 +9881,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -9440,7 +9958,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -9517,7 +10035,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -9594,7 +10112,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -9671,7 +10189,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -9748,7 +10266,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -9825,7 +10343,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -9902,7 +10420,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -9979,7 +10497,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -10056,7 +10574,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -10133,7 +10651,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -10210,7 +10728,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -10287,7 +10805,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -10364,7 +10882,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -10441,7 +10959,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -10518,7 +11036,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -10595,7 +11113,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -10672,7 +11190,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -10749,7 +11267,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -10826,7 +11344,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -10903,7 +11421,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -10980,7 +11498,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -11057,7 +11575,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -11134,7 +11652,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -11211,7 +11729,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -11288,7 +11806,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>48</v>
+        <v>157</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -11365,7 +11883,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -11442,7 +11960,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -11519,7 +12037,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -11596,7 +12114,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -11673,7 +12191,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -11750,7 +12268,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -11827,7 +12345,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -11904,7 +12422,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -11981,7 +12499,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -12058,7 +12576,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -12135,7 +12653,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>43</v>
+        <v>168</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -12212,7 +12730,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -12289,7 +12807,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -12366,7 +12884,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>128</v>
+        <v>171</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -12443,7 +12961,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -12520,7 +13038,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -12597,7 +13115,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>130</v>
+        <v>174</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -12674,7 +13192,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>79</v>
+        <v>175</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -12751,7 +13269,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -12828,7 +13346,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -12905,7 +13423,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -12982,7 +13500,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -13059,7 +13577,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>133</v>
+        <v>180</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -13136,7 +13654,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -13213,7 +13731,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -13290,7 +13808,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>36</v>
+        <v>183</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -13367,7 +13885,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -13444,7 +13962,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -13521,7 +14039,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>138</v>
+        <v>186</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -13598,7 +14116,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>139</v>
+        <v>187</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -13675,7 +14193,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>40</v>
+        <v>188</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -13752,7 +14270,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -13829,7 +14347,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>140</v>
+        <v>190</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -13906,7 +14424,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>136</v>
+        <v>191</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -13983,7 +14501,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>36</v>
+        <v>192</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -14060,7 +14578,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>141</v>
+        <v>193</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -14137,7 +14655,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>142</v>
+        <v>194</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -14214,7 +14732,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -14291,7 +14809,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -14368,7 +14886,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>143</v>
+        <v>197</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -14445,7 +14963,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>144</v>
+        <v>198</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -14522,7 +15040,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -14599,7 +15117,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -14676,7 +15194,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>69</v>
+        <v>201</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -14753,7 +15271,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -14830,7 +15348,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>147</v>
+        <v>203</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -14907,7 +15425,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -14984,7 +15502,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -15061,7 +15579,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>99</v>
+        <v>206</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -15138,7 +15656,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>149</v>
+        <v>207</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -15215,7 +15733,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>150</v>
+        <v>208</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -15292,7 +15810,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -15369,7 +15887,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -15446,7 +15964,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -15523,7 +16041,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>154</v>
+        <v>212</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -15600,7 +16118,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -15677,7 +16195,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>156</v>
+        <v>214</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -15754,7 +16272,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -15831,7 +16349,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>158</v>
+        <v>216</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -15908,7 +16426,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>159</v>
+        <v>217</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -15985,7 +16503,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>48</v>
+        <v>218</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -16062,7 +16580,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>107</v>
+        <v>219</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -16139,7 +16657,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -16216,7 +16734,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>161</v>
+        <v>221</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -16293,7 +16811,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>48</v>
+        <v>222</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -16370,7 +16888,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>42</v>
+        <v>223</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -16447,7 +16965,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -16524,7 +17042,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>163</v>
+        <v>225</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -16601,7 +17119,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>37</v>
+        <v>226</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -16678,7 +17196,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>164</v>
+        <v>227</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -16755,7 +17273,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>165</v>
+        <v>228</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -16832,7 +17350,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>166</v>
+        <v>229</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -16909,7 +17427,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>12</v>
+        <v>230</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -16986,7 +17504,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>167</v>
+        <v>231</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -17063,7 +17581,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>168</v>
+        <v>232</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -17140,7 +17658,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>169</v>
+        <v>233</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -17217,7 +17735,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -17294,7 +17812,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -17371,7 +17889,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>171</v>
+        <v>236</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -17448,7 +17966,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>172</v>
+        <v>237</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -17525,7 +18043,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>173</v>
+        <v>238</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -17602,7 +18120,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -17679,7 +18197,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>175</v>
+        <v>240</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -17756,7 +18274,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>176</v>
+        <v>241</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -17833,7 +18351,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>177</v>
+        <v>242</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -17910,7 +18428,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>12</v>
+        <v>243</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -17987,7 +18505,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>178</v>
+        <v>244</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -18064,7 +18582,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>179</v>
+        <v>245</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -18141,7 +18659,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -18218,7 +18736,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -18295,7 +18813,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>182</v>
+        <v>248</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -18372,7 +18890,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>183</v>
+        <v>249</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -18449,7 +18967,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>184</v>
+        <v>250</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -18526,7 +19044,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>185</v>
+        <v>251</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -18603,7 +19121,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>186</v>
+        <v>252</v>
       </c>
       <c r="C228">
         <v>0</v>
@@ -18680,7 +19198,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>187</v>
+        <v>253</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -18757,7 +19275,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>188</v>
+        <v>254</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -18834,7 +19352,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>174</v>
+        <v>255</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -18911,7 +19429,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>163</v>
+        <v>256</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -18988,7 +19506,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>37</v>
+        <v>257</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -19065,7 +19583,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>189</v>
+        <v>258</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -19142,7 +19660,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>190</v>
+        <v>259</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -19219,7 +19737,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -19296,7 +19814,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>192</v>
+        <v>261</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -19373,7 +19891,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>193</v>
+        <v>262</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -19450,7 +19968,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>194</v>
+        <v>263</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -19527,7 +20045,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>195</v>
+        <v>264</v>
       </c>
       <c r="C240">
         <v>0</v>
@@ -19604,7 +20122,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>37</v>
+        <v>265</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -19681,7 +20199,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>185</v>
+        <v>266</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -19758,7 +20276,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>186</v>
+        <v>267</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -19835,7 +20353,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>196</v>
+        <v>268</v>
       </c>
       <c r="C244">
         <v>0</v>
@@ -19912,7 +20430,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>197</v>
+        <v>269</v>
       </c>
       <c r="C245">
         <v>0</v>
@@ -19989,7 +20507,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>198</v>
+        <v>270</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -20066,7 +20584,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>199</v>
+        <v>271</v>
       </c>
       <c r="C247">
         <v>0</v>
@@ -20143,7 +20661,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>200</v>
+        <v>272</v>
       </c>
       <c r="C248">
         <v>0</v>
@@ -20220,7 +20738,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>201</v>
+        <v>273</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -20297,7 +20815,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>202</v>
+        <v>274</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -20374,7 +20892,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>203</v>
+        <v>275</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -20451,7 +20969,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>12</v>
+        <v>276</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -20528,7 +21046,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>204</v>
+        <v>277</v>
       </c>
       <c r="C253">
         <v>0</v>
@@ -20605,7 +21123,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>205</v>
+        <v>278</v>
       </c>
       <c r="C254">
         <v>0</v>
@@ -20682,7 +21200,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>163</v>
+        <v>279</v>
       </c>
       <c r="C255">
         <v>0</v>
@@ -20759,7 +21277,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>185</v>
+        <v>280</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -20836,7 +21354,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>186</v>
+        <v>281</v>
       </c>
       <c r="C257">
         <v>0</v>
@@ -20913,7 +21431,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>12</v>
+        <v>282</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -20990,7 +21508,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>12</v>
+        <v>283</v>
       </c>
       <c r="C259">
         <v>0</v>
@@ -21067,7 +21585,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>166</v>
+        <v>284</v>
       </c>
       <c r="C260">
         <v>0</v>
@@ -21144,7 +21662,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>206</v>
+        <v>285</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -21221,7 +21739,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>37</v>
+        <v>286</v>
       </c>
       <c r="C262">
         <v>0</v>
@@ -21298,7 +21816,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>163</v>
+        <v>287</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -21375,7 +21893,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>37</v>
+        <v>288</v>
       </c>
       <c r="C264">
         <v>0</v>
@@ -21452,7 +21970,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>166</v>
+        <v>289</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -21529,7 +22047,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>163</v>
+        <v>290</v>
       </c>
       <c r="C266">
         <v>0</v>
@@ -21606,7 +22124,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>37</v>
+        <v>291</v>
       </c>
       <c r="C267">
         <v>0</v>
@@ -21683,7 +22201,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="C268">
         <v>0</v>
@@ -21760,7 +22278,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>208</v>
+        <v>293</v>
       </c>
       <c r="C269">
         <v>0</v>
@@ -21837,7 +22355,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>209</v>
+        <v>294</v>
       </c>
       <c r="C270">
         <v>0</v>
@@ -21914,7 +22432,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>210</v>
+        <v>295</v>
       </c>
       <c r="C271">
         <v>0</v>
@@ -21991,7 +22509,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>211</v>
+        <v>296</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -22068,7 +22586,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>212</v>
+        <v>297</v>
       </c>
       <c r="C273">
         <v>0</v>
@@ -22145,7 +22663,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>37</v>
+        <v>298</v>
       </c>
       <c r="C274">
         <v>0</v>
@@ -22222,7 +22740,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>213</v>
+        <v>299</v>
       </c>
       <c r="C275">
         <v>0</v>
@@ -22299,7 +22817,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>159</v>
+        <v>300</v>
       </c>
       <c r="C276">
         <v>0</v>
@@ -22376,7 +22894,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>163</v>
+        <v>301</v>
       </c>
       <c r="C277">
         <v>0</v>
@@ -22453,7 +22971,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>214</v>
+        <v>302</v>
       </c>
       <c r="C278">
         <v>0</v>
@@ -22530,7 +23048,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>215</v>
+        <v>303</v>
       </c>
       <c r="C279">
         <v>0</v>
@@ -22607,7 +23125,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>182</v>
+        <v>304</v>
       </c>
       <c r="C280">
         <v>0</v>
@@ -22684,7 +23202,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>216</v>
+        <v>305</v>
       </c>
       <c r="C281">
         <v>0</v>
@@ -22761,7 +23279,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>37</v>
+        <v>306</v>
       </c>
       <c r="C282">
         <v>0</v>
@@ -22838,7 +23356,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>185</v>
+        <v>307</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -22915,7 +23433,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>186</v>
+        <v>308</v>
       </c>
       <c r="C284">
         <v>0</v>
@@ -22992,7 +23510,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>37</v>
+        <v>309</v>
       </c>
       <c r="C285">
         <v>0</v>
@@ -23069,7 +23587,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>163</v>
+        <v>310</v>
       </c>
       <c r="C286">
         <v>0</v>
@@ -23146,7 +23664,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>217</v>
+        <v>311</v>
       </c>
       <c r="C287">
         <v>0</v>
@@ -23223,7 +23741,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>218</v>
+        <v>312</v>
       </c>
       <c r="C288">
         <v>0</v>
@@ -23300,7 +23818,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>219</v>
+        <v>313</v>
       </c>
       <c r="C289">
         <v>0</v>
@@ -23377,7 +23895,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>220</v>
+        <v>314</v>
       </c>
       <c r="C290">
         <v>0</v>
@@ -23454,7 +23972,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>221</v>
+        <v>315</v>
       </c>
       <c r="C291">
         <v>0</v>
@@ -23531,7 +24049,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>166</v>
+        <v>316</v>
       </c>
       <c r="C292">
         <v>0</v>
@@ -23608,7 +24126,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>222</v>
+        <v>317</v>
       </c>
       <c r="C293">
         <v>0</v>
@@ -23685,7 +24203,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>223</v>
+        <v>318</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -23762,7 +24280,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>224</v>
+        <v>319</v>
       </c>
       <c r="C295">
         <v>0</v>
@@ -23839,7 +24357,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>163</v>
+        <v>320</v>
       </c>
       <c r="C296">
         <v>0</v>
@@ -23916,7 +24434,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>218</v>
+        <v>321</v>
       </c>
       <c r="C297">
         <v>0</v>
@@ -23993,7 +24511,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>225</v>
+        <v>322</v>
       </c>
       <c r="C298">
         <v>0</v>
@@ -24070,7 +24588,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>226</v>
+        <v>323</v>
       </c>
       <c r="C299">
         <v>0</v>
@@ -24147,7 +24665,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>227</v>
+        <v>324</v>
       </c>
       <c r="C300">
         <v>0</v>
@@ -24224,7 +24742,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>228</v>
+        <v>325</v>
       </c>
       <c r="C301">
         <v>0</v>
@@ -24301,7 +24819,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -24378,7 +24896,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>230</v>
+        <v>327</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -24455,7 +24973,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>37</v>
+        <v>328</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -24532,7 +25050,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>231</v>
+        <v>329</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -24609,7 +25127,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>159</v>
+        <v>330</v>
       </c>
       <c r="C306">
         <v>0</v>
@@ -24686,7 +25204,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>37</v>
+        <v>331</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -24763,7 +25281,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>37</v>
+        <v>332</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -24840,7 +25358,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>37</v>
+        <v>333</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -24917,7 +25435,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>166</v>
+        <v>334</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -24994,7 +25512,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>232</v>
+        <v>335</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -25071,7 +25589,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>233</v>
+        <v>336</v>
       </c>
       <c r="C312">
         <v>0</v>
@@ -25148,7 +25666,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>234</v>
+        <v>337</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -25225,7 +25743,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>149</v>
+        <v>338</v>
       </c>
       <c r="C314">
         <v>0</v>
@@ -25302,7 +25820,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>150</v>
+        <v>339</v>
       </c>
       <c r="C315">
         <v>0</v>
@@ -25379,7 +25897,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>37</v>
+        <v>340</v>
       </c>
       <c r="C316">
         <v>0</v>
@@ -25456,7 +25974,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>235</v>
+        <v>341</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -25533,7 +26051,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>37</v>
+        <v>342</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -25610,7 +26128,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>163</v>
+        <v>343</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -25687,7 +26205,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>37</v>
+        <v>344</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -25764,7 +26282,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>166</v>
+        <v>345</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -25841,7 +26359,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>166</v>
+        <v>346</v>
       </c>
       <c r="C322">
         <v>0</v>
@@ -25918,7 +26436,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>12</v>
+        <v>347</v>
       </c>
       <c r="C323">
         <v>0</v>
@@ -25995,7 +26513,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>236</v>
+        <v>348</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -26072,7 +26590,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>237</v>
+        <v>349</v>
       </c>
       <c r="C325">
         <v>0</v>
@@ -26149,7 +26667,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>185</v>
+        <v>350</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -26226,7 +26744,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>186</v>
+        <v>351</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -26303,7 +26821,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>166</v>
+        <v>352</v>
       </c>
       <c r="C328">
         <v>0</v>
@@ -26380,7 +26898,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>163</v>
+        <v>353</v>
       </c>
       <c r="C329">
         <v>0</v>
@@ -26457,7 +26975,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>37</v>
+        <v>354</v>
       </c>
       <c r="C330">
         <v>0</v>
@@ -26534,7 +27052,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>159</v>
+        <v>355</v>
       </c>
       <c r="C331">
         <v>0</v>
@@ -26611,7 +27129,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>114</v>
+        <v>356</v>
       </c>
       <c r="C332">
         <v>0</v>
@@ -26688,7 +27206,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>238</v>
+        <v>357</v>
       </c>
       <c r="C333">
         <v>0</v>
@@ -26765,7 +27283,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>239</v>
+        <v>358</v>
       </c>
       <c r="C334">
         <v>0</v>
@@ -26842,7 +27360,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>240</v>
+        <v>359</v>
       </c>
       <c r="C335">
         <v>0</v>
@@ -26919,7 +27437,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>241</v>
+        <v>360</v>
       </c>
       <c r="C336">
         <v>0</v>
@@ -26996,7 +27514,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>56</v>
+        <v>361</v>
       </c>
       <c r="C337">
         <v>0</v>
@@ -27073,7 +27591,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>12</v>
+        <v>362</v>
       </c>
       <c r="C338">
         <v>0</v>
@@ -27150,7 +27668,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>242</v>
+        <v>363</v>
       </c>
       <c r="C339">
         <v>0</v>
@@ -27227,7 +27745,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>37</v>
+        <v>364</v>
       </c>
       <c r="C340">
         <v>0</v>
@@ -27304,7 +27822,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>243</v>
+        <v>365</v>
       </c>
       <c r="C341">
         <v>0</v>
@@ -27381,7 +27899,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>12</v>
+        <v>366</v>
       </c>
       <c r="C342">
         <v>0</v>
@@ -27458,7 +27976,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>244</v>
+        <v>367</v>
       </c>
       <c r="C343">
         <v>0</v>
@@ -27535,7 +28053,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>245</v>
+        <v>368</v>
       </c>
       <c r="C344">
         <v>0</v>
@@ -27612,7 +28130,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>246</v>
+        <v>369</v>
       </c>
       <c r="C345">
         <v>0</v>
@@ -27689,7 +28207,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>247</v>
+        <v>370</v>
       </c>
       <c r="C346">
         <v>0</v>
@@ -27766,7 +28284,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>12</v>
+        <v>371</v>
       </c>
       <c r="C347">
         <v>0</v>
@@ -27843,7 +28361,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>163</v>
+        <v>372</v>
       </c>
       <c r="C348">
         <v>0</v>
@@ -27920,7 +28438,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>37</v>
+        <v>373</v>
       </c>
       <c r="C349">
         <v>0</v>
@@ -27997,7 +28515,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>146</v>
+        <v>374</v>
       </c>
       <c r="C350">
         <v>0</v>
@@ -28074,7 +28592,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>34</v>
+        <v>375</v>
       </c>
       <c r="C351">
         <v>0</v>
@@ -28151,7 +28669,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>35</v>
+        <v>376</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -28228,7 +28746,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>12</v>
+        <v>377</v>
       </c>
       <c r="C353">
         <v>0</v>
@@ -28305,7 +28823,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>114</v>
+        <v>378</v>
       </c>
       <c r="C354">
         <v>0</v>
@@ -28382,7 +28900,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>248</v>
+        <v>379</v>
       </c>
       <c r="C355">
         <v>0</v>
@@ -28459,7 +28977,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>249</v>
+        <v>380</v>
       </c>
       <c r="C356">
         <v>0</v>
@@ -28536,7 +29054,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>250</v>
+        <v>381</v>
       </c>
       <c r="C357">
         <v>0</v>
@@ -28613,7 +29131,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>37</v>
+        <v>382</v>
       </c>
       <c r="C358">
         <v>0</v>
@@ -28690,7 +29208,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>12</v>
+        <v>383</v>
       </c>
       <c r="C359">
         <v>0</v>
@@ -28767,7 +29285,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>163</v>
+        <v>384</v>
       </c>
       <c r="C360">
         <v>0</v>
@@ -28844,7 +29362,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>251</v>
+        <v>385</v>
       </c>
       <c r="C361">
         <v>0</v>
@@ -28921,7 +29439,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>12</v>
+        <v>386</v>
       </c>
       <c r="C362">
         <v>0</v>
@@ -28998,7 +29516,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>37</v>
+        <v>387</v>
       </c>
       <c r="C363">
         <v>0</v>
@@ -29075,7 +29593,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>37</v>
+        <v>388</v>
       </c>
       <c r="C364">
         <v>0</v>
@@ -29152,7 +29670,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>182</v>
+        <v>389</v>
       </c>
       <c r="C365">
         <v>0</v>
@@ -29229,7 +29747,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>216</v>
+        <v>390</v>
       </c>
       <c r="C366">
         <v>0</v>
@@ -29306,7 +29824,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>252</v>
+        <v>391</v>
       </c>
       <c r="C367">
         <v>0</v>
@@ -29383,7 +29901,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>253</v>
+        <v>392</v>
       </c>
       <c r="C368">
         <v>0</v>
@@ -29460,7 +29978,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>254</v>
+        <v>393</v>
       </c>
       <c r="C369">
         <v>0</v>
@@ -29537,7 +30055,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>255</v>
+        <v>394</v>
       </c>
       <c r="C370">
         <v>0</v>
@@ -29614,7 +30132,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>42</v>
+        <v>395</v>
       </c>
       <c r="C371">
         <v>0</v>
@@ -29691,7 +30209,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>256</v>
+        <v>396</v>
       </c>
       <c r="C372">
         <v>0</v>
@@ -29768,7 +30286,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>257</v>
+        <v>397</v>
       </c>
       <c r="C373">
         <v>0</v>
